--- a/report_template/dailyReport2.xlsx
+++ b/report_template/dailyReport2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\Datalogger2\report_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376D0A92-C84A-472E-B344-CC71FC81DEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29919C41-ECC9-47F3-A070-693731693C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8246" yWindow="377" windowWidth="16628" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1937" yWindow="3051" windowWidth="24686" windowHeight="13055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
@@ -123,6 +123,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="177" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="178" formatCode="[$-1000000]h:mm;@"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -268,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -290,9 +294,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -329,6 +330,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,47 +634,47 @@
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="13.1640625" customWidth="1"/>
-    <col min="16" max="16" width="14.4140625" style="12" customWidth="1"/>
-    <col min="17" max="17" width="11.33203125" style="12" customWidth="1"/>
+    <col min="16" max="16" width="14.4140625" style="11" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
@@ -715,490 +722,490 @@
       <c r="O3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="9"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
     </row>
     <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="9"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="9"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
     </row>
     <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="9"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="9"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="9"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="9"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
       <c r="U15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="9"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="9"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="9"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="9"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="9"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="9"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="9"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="9"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="9"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="9"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="9"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="9"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="9"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
@@ -1251,8 +1258,8 @@
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
@@ -1305,8 +1312,8 @@
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
@@ -1359,22 +1366,22 @@
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="19"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="18"/>
       <c r="K32" s="8">
         <f>SUM(K4:K28)</f>
         <v>0</v>
@@ -1392,164 +1399,164 @@
         <f>(O4-O28)</f>
         <v>0</v>
       </c>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
     </row>
     <row r="35" spans="1:13" ht="9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
     </row>
     <row r="36" spans="1:13" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
     </row>
     <row r="37" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="16" t="s">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
     </row>
     <row r="38" spans="1:13" ht="52.5" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
     </row>
     <row r="39" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
     </row>
     <row r="40" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
     </row>
     <row r="41" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
     </row>
     <row r="42" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B43" s="1"/>

--- a/report_template/dailyReport2.xlsx
+++ b/report_template/dailyReport2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\Datalogger2\report_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB89BADB-02B0-463A-B6EC-3CE582F0DD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE05761-74A6-4E96-A234-B04AEA328136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{1FF98DE7-DF0E-49E7-AD88-0362929A6F74}"/>
   </bookViews>
@@ -152,6 +152,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="[$-101042A]d\ mmmm\ yyyy;@"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -324,7 +327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -388,6 +391,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,8 +766,8 @@
       <c r="L2" s="21"/>
       <c r="M2" s="21"/>
       <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
     </row>
     <row r="3" spans="1:16" ht="69.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
@@ -2231,12 +2237,13 @@
       <c r="O34" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A34:H34"/>
     <mergeCell ref="I34:O34"/>
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="O2:P2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/report_template/dailyReport2.xlsx
+++ b/report_template/dailyReport2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\Datalogger2\report_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repo\Datalogger2\report_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE05761-74A6-4E96-A234-B04AEA328136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479872A2-160C-40B3-BE10-AD3B57DE4DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{1FF98DE7-DF0E-49E7-AD88-0362929A6F74}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1FF98DE7-DF0E-49E7-AD88-0362929A6F74}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="[$-101042A]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="177" formatCode="[$-1010000]d/m/yyyy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -710,26 +710,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BEFEB7-514D-4118-8687-1DEFEE9BACBE}">
   <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultColWidth="15.765625" defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="15.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.15234375" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" customWidth="1"/>
-    <col min="3" max="3" width="11.61328125" customWidth="1"/>
-    <col min="4" max="4" width="7.84375" customWidth="1"/>
-    <col min="5" max="5" width="6.84375" customWidth="1"/>
-    <col min="6" max="6" width="7.15234375" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" customWidth="1"/>
+    <col min="2" max="2" width="5.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" customWidth="1"/>
+    <col min="5" max="5" width="6.81640625" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="7.61328125" customWidth="1"/>
-    <col min="9" max="9" width="5.61328125" customWidth="1"/>
-    <col min="10" max="10" width="7.84375" customWidth="1"/>
-    <col min="11" max="11" width="7.15234375" customWidth="1"/>
-    <col min="12" max="13" width="6.84375" customWidth="1"/>
-    <col min="14" max="14" width="9.84375" customWidth="1"/>
-    <col min="15" max="15" width="10.61328125" customWidth="1"/>
-    <col min="16" max="16" width="10.15234375" customWidth="1"/>
+    <col min="8" max="8" width="7.6328125" customWidth="1"/>
+    <col min="9" max="9" width="5.6328125" customWidth="1"/>
+    <col min="10" max="10" width="7.81640625" customWidth="1"/>
+    <col min="11" max="11" width="7.1796875" customWidth="1"/>
+    <col min="12" max="13" width="6.81640625" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" customWidth="1"/>
+    <col min="15" max="15" width="10.6328125" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
@@ -749,7 +749,7 @@
       <c r="O1" s="20"/>
       <c r="P1" s="20"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
@@ -769,7 +769,7 @@
       <c r="O2" s="22"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:16" ht="69.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="69.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -819,7 +819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="13">
         <v>0</v>
       </c>
@@ -869,7 +869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="13">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -919,7 +919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="13">
         <v>8.3333333333333329E-2</v>
       </c>
@@ -969,7 +969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="13">
         <v>0.125</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="13">
         <v>0.16666666666666666</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="13">
         <v>0.20833333333333334</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="13">
         <v>0.25</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="13">
         <v>0.29166666666666669</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="13">
         <v>0.33333333333333331</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="13">
         <v>0.375</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" s="13">
         <v>0.41666666666666669</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="13">
         <v>0.45833333333333331</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="13">
         <v>0.5</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="13">
         <v>0.54166666666666663</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="13">
         <v>0.58333333333333337</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="13">
         <v>0.625</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" s="13">
         <v>0.66666666666666663</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="13">
         <v>0.70833333333333337</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22" s="13">
         <v>0.75</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" s="13">
         <v>0.79166666666666663</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24" s="13">
         <v>0.83333333333333337</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25" s="13">
         <v>0.875</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="13">
         <v>0.91666666666666663</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="13">
         <v>0.95833333333333337</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
         <v>3</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
         <v>4</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="14" t="s">
         <v>5</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="14" t="s">
         <v>25</v>
       </c>
@@ -2171,7 +2171,7 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>0</v>
       </c>
@@ -2195,7 +2195,7 @@
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" spans="1:16" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="17" t="s">
         <v>8</v>
       </c>
@@ -2215,7 +2215,7 @@
       <c r="O33" s="18"/>
       <c r="P33" s="19"/>
     </row>
-    <row r="34" spans="1:16" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="15" t="s">
         <v>9</v>
       </c>

--- a/report_template/dailyReport2.xlsx
+++ b/report_template/dailyReport2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repo\Datalogger2\report_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479872A2-160C-40B3-BE10-AD3B57DE4DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32835668-57B0-4279-B624-3BF7DEF1F749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1FF98DE7-DF0E-49E7-AD88-0362929A6F74}"/>
   </bookViews>
@@ -47,13 +47,7 @@
     <t>TEMP</t>
   </si>
   <si>
-    <t>AVG</t>
-  </si>
-  <si>
     <t>MAX</t>
-  </si>
-  <si>
-    <t>MIN</t>
   </si>
   <si>
     <t>BẢNG GHI CHÉP SỐ LIỆU QUAN TRẮC CHẤT LƯỢNG NƯỚC XẢ THẢI PHÂN KHU CÔNG NGHIỆP FORMOSA</t>
@@ -145,6 +139,14 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AVG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -153,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="176" formatCode="[$-1010000]d/m/yyyy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,12 +208,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -368,7 +364,7 @@
     <xf numFmtId="20" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -392,7 +388,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -731,7 +727,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -751,7 +747,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -777,46 +773,46 @@
         <v>2</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="G3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="J3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="K3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="12" t="s">
+      <c r="O3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="P3" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
@@ -824,49 +820,49 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
@@ -874,49 +870,49 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
@@ -924,49 +920,49 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
@@ -974,49 +970,49 @@
         <v>0.125</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
@@ -1024,49 +1020,49 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
@@ -1074,49 +1070,49 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
@@ -1124,49 +1120,49 @@
         <v>0.25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
@@ -1174,49 +1170,49 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
@@ -1224,49 +1220,49 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
@@ -1274,49 +1270,49 @@
         <v>0.375</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
@@ -1324,49 +1320,49 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
@@ -1374,49 +1370,49 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
@@ -1424,49 +1420,49 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
@@ -1474,49 +1470,49 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
@@ -1524,49 +1520,49 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
@@ -1574,49 +1570,49 @@
         <v>0.625</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
@@ -1624,49 +1620,49 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
@@ -1674,49 +1670,49 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
@@ -1724,49 +1720,49 @@
         <v>0.75</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
@@ -1774,49 +1770,49 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
@@ -1824,49 +1820,49 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
@@ -1874,49 +1870,49 @@
         <v>0.875</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
@@ -1924,49 +1920,49 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
@@ -1974,154 +1970,154 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="14" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2141,7 +2137,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3">
@@ -2168,18 +2164,24 @@
         <f>SUM(N4:N27)</f>
         <v>0</v>
       </c>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
+      <c r="O31" s="7">
+        <f>SUM(N4:N27)</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="7">
+        <f>SUM(C4:C27)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -2197,7 +2199,7 @@
     </row>
     <row r="33" spans="1:16" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -2217,7 +2219,7 @@
     </row>
     <row r="34" spans="1:16" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -2227,7 +2229,7 @@
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
       <c r="I34" s="16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J34" s="16"/>
       <c r="K34" s="16"/>

--- a/report_template/dailyReport2.xlsx
+++ b/report_template/dailyReport2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repo\Datalogger2\report_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32835668-57B0-4279-B624-3BF7DEF1F749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CBFE91-AB91-45F5-AB14-07EF8A1F0608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1FF98DE7-DF0E-49E7-AD88-0362929A6F74}"/>
   </bookViews>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>26</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
